--- a/artfynd/A 53555-2025 artfynd.xlsx
+++ b/artfynd/A 53555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129951691</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129951748</v>
       </c>
       <c r="B3" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129951705</v>
       </c>
       <c r="B4" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>129951723</v>
       </c>
       <c r="B5" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129951741</v>
       </c>
       <c r="B6" t="n">
-        <v>97667</v>
+        <v>97671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53555-2025 artfynd.xlsx
+++ b/artfynd/A 53555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129951691</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129951748</v>
       </c>
       <c r="B3" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129951705</v>
       </c>
       <c r="B4" t="n">
-        <v>92320</v>
+        <v>92323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>129951723</v>
       </c>
       <c r="B5" t="n">
-        <v>92320</v>
+        <v>92323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129951741</v>
       </c>
       <c r="B6" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53555-2025 artfynd.xlsx
+++ b/artfynd/A 53555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129951691</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129951748</v>
       </c>
       <c r="B3" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129951705</v>
       </c>
       <c r="B4" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129951723</v>
+        <v>129951741</v>
       </c>
       <c r="B5" t="n">
-        <v>92323</v>
+        <v>97675</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,26 +1058,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1085,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523664</v>
+        <v>523661</v>
       </c>
       <c r="R5" t="n">
-        <v>6663141</v>
+        <v>6663195</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,6 +1132,11 @@
           <t>2025-12-02</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 100 m2 har snitslats av som hänsyn runt växtplatsen! Mycket ovanlig åtgärd.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1141,21 +1155,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>mest mossa</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>vid gruvhål # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1173,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129951741</v>
+        <v>129951723</v>
       </c>
       <c r="B6" t="n">
-        <v>97674</v>
+        <v>92324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,35 +1183,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1220,10 +1210,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523661</v>
+        <v>523664</v>
       </c>
       <c r="R6" t="n">
-        <v>6663195</v>
+        <v>6663141</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1258,11 +1248,6 @@
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca 100 m2 har snitslats av som hänsyn runt växtplatsen! Mycket ovanlig åtgärd.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1281,6 +1266,21 @@
       <c r="AI6" t="inlineStr">
         <is>
           <t>mest mossa</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>vid gruvhål # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 53555-2025 artfynd.xlsx
+++ b/artfynd/A 53555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129951691</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129951748</v>
       </c>
       <c r="B3" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129951705</v>
       </c>
       <c r="B4" t="n">
-        <v>92324</v>
+        <v>92341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>129951741</v>
       </c>
       <c r="B5" t="n">
-        <v>97675</v>
+        <v>97692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>129951723</v>
       </c>
       <c r="B6" t="n">
-        <v>92324</v>
+        <v>92341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53555-2025 artfynd.xlsx
+++ b/artfynd/A 53555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129951691</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129951748</v>
       </c>
       <c r="B3" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129951705</v>
       </c>
       <c r="B4" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>129951723</v>
       </c>
       <c r="B5" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129951741</v>
       </c>
       <c r="B6" t="n">
-        <v>97708</v>
+        <v>97710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53555-2025 artfynd.xlsx
+++ b/artfynd/A 53555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129951691</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129951748</v>
       </c>
       <c r="B3" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129951705</v>
       </c>
       <c r="B4" t="n">
-        <v>92359</v>
+        <v>92446</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129951723</v>
+        <v>129951741</v>
       </c>
       <c r="B5" t="n">
-        <v>92359</v>
+        <v>97797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,26 +1058,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1085,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523664</v>
+        <v>523661</v>
       </c>
       <c r="R5" t="n">
-        <v>6663141</v>
+        <v>6663195</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,6 +1132,11 @@
           <t>2025-12-02</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 100 m2 har snitslats av som hänsyn runt växtplatsen! Mycket ovanlig åtgärd.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1141,21 +1155,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>mest mossa</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>vid gruvhål # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1173,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129951741</v>
+        <v>129951723</v>
       </c>
       <c r="B6" t="n">
-        <v>97710</v>
+        <v>92446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,35 +1183,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1220,10 +1210,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523661</v>
+        <v>523664</v>
       </c>
       <c r="R6" t="n">
-        <v>6663195</v>
+        <v>6663141</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1258,11 +1248,6 @@
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca 100 m2 har snitslats av som hänsyn runt växtplatsen! Mycket ovanlig åtgärd.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1281,6 +1266,21 @@
       <c r="AI6" t="inlineStr">
         <is>
           <t>mest mossa</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>vid gruvhål # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 53555-2025 artfynd.xlsx
+++ b/artfynd/A 53555-2025 artfynd.xlsx
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129951741</v>
+        <v>129951723</v>
       </c>
       <c r="B5" t="n">
-        <v>97797</v>
+        <v>92446</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,35 +1058,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1094,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523661</v>
+        <v>523664</v>
       </c>
       <c r="R5" t="n">
-        <v>6663195</v>
+        <v>6663141</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1132,11 +1123,6 @@
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 100 m2 har snitslats av som hänsyn runt växtplatsen! Mycket ovanlig åtgärd.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1155,6 +1141,21 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>mest mossa</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>vid gruvhål # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1172,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129951723</v>
+        <v>129951741</v>
       </c>
       <c r="B6" t="n">
-        <v>92446</v>
+        <v>97797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,26 +1184,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1210,10 +1220,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523664</v>
+        <v>523661</v>
       </c>
       <c r="R6" t="n">
-        <v>6663141</v>
+        <v>6663195</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1248,6 +1258,11 @@
           <t>2025-12-02</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca 100 m2 har snitslats av som hänsyn runt växtplatsen! Mycket ovanlig åtgärd.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1266,21 +1281,6 @@
       <c r="AI6" t="inlineStr">
         <is>
           <t>mest mossa</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>vid gruvhål # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 53555-2025 artfynd.xlsx
+++ b/artfynd/A 53555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129951691</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129951748</v>
       </c>
       <c r="B3" t="n">
-        <v>93010</v>
+        <v>92923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129951705</v>
       </c>
       <c r="B4" t="n">
-        <v>92446</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>129951723</v>
       </c>
       <c r="B5" t="n">
-        <v>92446</v>
+        <v>92359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129951741</v>
       </c>
       <c r="B6" t="n">
-        <v>97797</v>
+        <v>97710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53555-2025 artfynd.xlsx
+++ b/artfynd/A 53555-2025 artfynd.xlsx
@@ -675,46 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129951691</v>
+        <v>129951705</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523182</v>
+        <v>523524</v>
       </c>
       <c r="R2" t="n">
-        <v>6663451</v>
+        <v>6663318</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -778,6 +769,26 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>mest mossa</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129951748</v>
+        <v>129951723</v>
       </c>
       <c r="B3" t="n">
-        <v>93010</v>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523335</v>
+        <v>523664</v>
       </c>
       <c r="R3" t="n">
-        <v>6663435</v>
+        <v>6663141</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,14 +902,19 @@
           <t>mest mossa</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>grovt gammalt träd</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>grovt gammalt träd</t>
+          <t>vid gruvhål # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -916,32 +932,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129951705</v>
+        <v>129951748</v>
       </c>
       <c r="B4" t="n">
-        <v>92446</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523524</v>
+        <v>523335</v>
       </c>
       <c r="R4" t="n">
-        <v>6663318</v>
+        <v>6663435</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1012,24 +1028,14 @@
           <t>mest mossa</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>grovt gammalt träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>grovt gammalt träd</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1047,37 +1053,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129951723</v>
+        <v>129951691</v>
       </c>
       <c r="B5" t="n">
-        <v>92446</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1085,10 +1100,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523664</v>
+        <v>523182</v>
       </c>
       <c r="R5" t="n">
-        <v>6663141</v>
+        <v>6663451</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1141,21 +1156,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>mest mossa</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>vid gruvhål # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1176,7 +1176,7 @@
         <v>129951741</v>
       </c>
       <c r="B6" t="n">
-        <v>97797</v>
+        <v>97989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53555-2025 artfynd.xlsx
+++ b/artfynd/A 53555-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129951705</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -929,6 +939,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129951723</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129951748</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1170,6 +1190,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129951691</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1295,8 +1320,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129951741</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>